--- a/videos/003_cs_data_science_longitudinal_data_visualization/graficos_legacy.xlsx
+++ b/videos/003_cs_data_science_longitudinal_data_visualization/graficos_legacy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/content_youtube_tiktok_linkedin/linkedin_posts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/003_cs_data_science_longitudinal_data_visualization/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="288" documentId="11_F25DC773A252ABDACC1048F711DA615C5ADE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943D2A40-81BB-48FB-871A-41F80E472769}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="a1" sheetId="1" r:id="rId1"/>
@@ -331,37 +331,37 @@
                   <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197.25</c:v>
+                  <c:v>195.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>191.11250000000001</c:v>
+                  <c:v>202.01250000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>197.66812500000003</c:v>
+                  <c:v>201.11312500000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.55153125000004</c:v>
+                  <c:v>206.16878125000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>208.37910781250005</c:v>
+                  <c:v>216.47722031250004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>217.79806320312505</c:v>
+                  <c:v>228.30108132812504</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>223.6879663632813</c:v>
+                  <c:v>235.71613539453131</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>215.87236468144539</c:v>
+                  <c:v>248.50194216425788</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>229.66598291551767</c:v>
+                  <c:v>242.92703927247078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>232.14928206129358</c:v>
+                  <c:v>247.07339123609432</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>232.75674616435828</c:v>
+                  <c:v>255.42706079789906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -535,37 +535,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>168.15</c:v>
+                  <c:v>160.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179.5575</c:v>
+                  <c:v>162.94500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>185.53537500000002</c:v>
+                  <c:v>175.09225000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>192.81214375000002</c:v>
+                  <c:v>182.84686250000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>194.45275093750004</c:v>
+                  <c:v>186.98920562500004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>207.17538848437505</c:v>
+                  <c:v>194.33866590625004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>222.53415790859381</c:v>
+                  <c:v>198.05559920156256</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>237.6608658040235</c:v>
+                  <c:v>207.95837916164069</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>245.54390909422469</c:v>
+                  <c:v>221.35629811972274</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>256.82110454893592</c:v>
+                  <c:v>233.42411302570889</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -739,37 +739,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>107</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.350000000000009</c:v>
+                  <c:v>115.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>96.06750000000001</c:v>
+                  <c:v>103.7475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99.870875000000012</c:v>
+                  <c:v>94.934875000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>99.864418750000013</c:v>
+                  <c:v>96.681618750000013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>106.85763968750001</c:v>
+                  <c:v>103.51569968750002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>105.20052167187502</c:v>
+                  <c:v>89.691484671875017</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>108.46054775546878</c:v>
+                  <c:v>82.176058905468778</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100.88357514324223</c:v>
+                  <c:v>82.284861850742217</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.92775390040434</c:v>
+                  <c:v>68.399104943279326</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>92.774141595424567</c:v>
+                  <c:v>51.819060190443295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1120,37 +1120,37 @@
                   <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197.25</c:v>
+                  <c:v>195.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>191.11250000000001</c:v>
+                  <c:v>202.01250000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>197.66812500000003</c:v>
+                  <c:v>201.11312500000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.55153125000004</c:v>
+                  <c:v>206.16878125000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>208.37910781250005</c:v>
+                  <c:v>216.47722031250004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>217.79806320312505</c:v>
+                  <c:v>228.30108132812504</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>223.6879663632813</c:v>
+                  <c:v>235.71613539453131</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>215.87236468144539</c:v>
+                  <c:v>248.50194216425788</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>229.66598291551767</c:v>
+                  <c:v>242.92703927247078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>232.14928206129358</c:v>
+                  <c:v>247.07339123609432</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>232.75674616435828</c:v>
+                  <c:v>255.42706079789906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,37 +1307,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>168.15</c:v>
+                  <c:v>160.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179.5575</c:v>
+                  <c:v>162.94500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>185.53537500000002</c:v>
+                  <c:v>175.09225000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>192.81214375000002</c:v>
+                  <c:v>182.84686250000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>194.45275093750004</c:v>
+                  <c:v>186.98920562500004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>207.17538848437505</c:v>
+                  <c:v>194.33866590625004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>222.53415790859381</c:v>
+                  <c:v>198.05559920156256</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>237.6608658040235</c:v>
+                  <c:v>207.95837916164069</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>245.54390909422469</c:v>
+                  <c:v>221.35629811972274</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>256.82110454893592</c:v>
+                  <c:v>233.42411302570889</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1494,37 +1494,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>107</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.350000000000009</c:v>
+                  <c:v>115.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>96.06750000000001</c:v>
+                  <c:v>103.7475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99.870875000000012</c:v>
+                  <c:v>94.934875000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>99.864418750000013</c:v>
+                  <c:v>96.681618750000013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>106.85763968750001</c:v>
+                  <c:v>103.51569968750002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>105.20052167187502</c:v>
+                  <c:v>89.691484671875017</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>108.46054775546878</c:v>
+                  <c:v>82.176058905468778</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100.88357514324223</c:v>
+                  <c:v>82.284861850742217</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.92775390040434</c:v>
+                  <c:v>68.399104943279326</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>92.774141595424567</c:v>
+                  <c:v>51.819060190443295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2015,13 +2015,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>197.25</c:v>
+                  <c:v>195.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>107</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2148,13 +2148,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>191.11250000000001</c:v>
+                  <c:v>202.01250000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>168.15</c:v>
+                  <c:v>160.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.350000000000009</c:v>
+                  <c:v>115.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2281,13 +2281,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>197.66812500000003</c:v>
+                  <c:v>201.11312500000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>179.5575</c:v>
+                  <c:v>162.94500000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96.06750000000001</c:v>
+                  <c:v>103.7475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2414,13 +2414,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>196.55153125000004</c:v>
+                  <c:v>206.16878125000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>185.53537500000002</c:v>
+                  <c:v>175.09225000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99.870875000000012</c:v>
+                  <c:v>94.934875000000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2547,13 +2547,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>208.37910781250005</c:v>
+                  <c:v>216.47722031250004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.81214375000002</c:v>
+                  <c:v>182.84686250000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99.864418750000013</c:v>
+                  <c:v>96.681618750000013</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2685,13 +2685,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>217.79806320312505</c:v>
+                  <c:v>228.30108132812504</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>194.45275093750004</c:v>
+                  <c:v>186.98920562500004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>106.85763968750001</c:v>
+                  <c:v>103.51569968750002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2823,13 +2823,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>223.6879663632813</c:v>
+                  <c:v>235.71613539453131</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>207.17538848437505</c:v>
+                  <c:v>194.33866590625004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>105.20052167187502</c:v>
+                  <c:v>89.691484671875017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2961,13 +2961,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>215.87236468144539</c:v>
+                  <c:v>248.50194216425788</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>222.53415790859381</c:v>
+                  <c:v>198.05559920156256</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>108.46054775546878</c:v>
+                  <c:v>82.176058905468778</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3099,13 +3099,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>229.66598291551767</c:v>
+                  <c:v>242.92703927247078</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>237.6608658040235</c:v>
+                  <c:v>207.95837916164069</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100.88357514324223</c:v>
+                  <c:v>82.284861850742217</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3237,13 +3237,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>232.14928206129358</c:v>
+                  <c:v>247.07339123609432</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>245.54390909422469</c:v>
+                  <c:v>221.35629811972274</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96.92775390040434</c:v>
+                  <c:v>68.399104943279326</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3375,13 +3375,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>232.75674616435828</c:v>
+                  <c:v>255.42706079789906</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>256.82110454893592</c:v>
+                  <c:v>233.42411302570889</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>92.774141595424567</c:v>
+                  <c:v>51.819060190443295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3722,37 +3722,37 @@
                   <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197.25</c:v>
+                  <c:v>195.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>191.11250000000001</c:v>
+                  <c:v>202.01250000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>197.66812500000003</c:v>
+                  <c:v>201.11312500000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.55153125000004</c:v>
+                  <c:v>206.16878125000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>208.37910781250005</c:v>
+                  <c:v>216.47722031250004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>217.79806320312505</c:v>
+                  <c:v>228.30108132812504</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>223.6879663632813</c:v>
+                  <c:v>235.71613539453131</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>215.87236468144539</c:v>
+                  <c:v>248.50194216425788</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>229.66598291551767</c:v>
+                  <c:v>242.92703927247078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>232.14928206129358</c:v>
+                  <c:v>247.07339123609432</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>232.75674616435828</c:v>
+                  <c:v>255.42706079789906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3910,37 +3910,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>168.15</c:v>
+                  <c:v>160.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179.5575</c:v>
+                  <c:v>162.94500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>185.53537500000002</c:v>
+                  <c:v>175.09225000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>192.81214375000002</c:v>
+                  <c:v>182.84686250000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>194.45275093750004</c:v>
+                  <c:v>186.98920562500004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>207.17538848437505</c:v>
+                  <c:v>194.33866590625004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>222.53415790859381</c:v>
+                  <c:v>198.05559920156256</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>237.6608658040235</c:v>
+                  <c:v>207.95837916164069</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>245.54390909422469</c:v>
+                  <c:v>221.35629811972274</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>256.82110454893592</c:v>
+                  <c:v>233.42411302570889</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4098,37 +4098,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>107</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.350000000000009</c:v>
+                  <c:v>115.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>96.06750000000001</c:v>
+                  <c:v>103.7475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99.870875000000012</c:v>
+                  <c:v>94.934875000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>99.864418750000013</c:v>
+                  <c:v>96.681618750000013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>106.85763968750001</c:v>
+                  <c:v>103.51569968750002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>105.20052167187502</c:v>
+                  <c:v>89.691484671875017</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>108.46054775546878</c:v>
+                  <c:v>82.176058905468778</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100.88357514324223</c:v>
+                  <c:v>82.284861850742217</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.92775390040434</c:v>
+                  <c:v>68.399104943279326</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>92.774141595424567</c:v>
+                  <c:v>51.819060190443295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4466,37 +4466,37 @@
                   <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197.25</c:v>
+                  <c:v>195.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>191.11250000000001</c:v>
+                  <c:v>202.01250000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>197.66812500000003</c:v>
+                  <c:v>201.11312500000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.55153125000004</c:v>
+                  <c:v>206.16878125000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>208.37910781250005</c:v>
+                  <c:v>216.47722031250004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>217.79806320312505</c:v>
+                  <c:v>228.30108132812504</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>223.6879663632813</c:v>
+                  <c:v>235.71613539453131</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>215.87236468144539</c:v>
+                  <c:v>248.50194216425788</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>229.66598291551767</c:v>
+                  <c:v>242.92703927247078</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>232.14928206129358</c:v>
+                  <c:v>247.07339123609432</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>232.75674616435828</c:v>
+                  <c:v>255.42706079789906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4653,37 +4653,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>163</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>168.15</c:v>
+                  <c:v>160.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>179.5575</c:v>
+                  <c:v>162.94500000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>185.53537500000002</c:v>
+                  <c:v>175.09225000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>192.81214375000002</c:v>
+                  <c:v>182.84686250000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>194.45275093750004</c:v>
+                  <c:v>186.98920562500004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>207.17538848437505</c:v>
+                  <c:v>194.33866590625004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>222.53415790859381</c:v>
+                  <c:v>198.05559920156256</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>237.6608658040235</c:v>
+                  <c:v>207.95837916164069</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>245.54390909422469</c:v>
+                  <c:v>221.35629811972274</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>256.82110454893592</c:v>
+                  <c:v>233.42411302570889</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4840,37 +4840,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>107</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.350000000000009</c:v>
+                  <c:v>115.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>96.06750000000001</c:v>
+                  <c:v>103.7475</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99.870875000000012</c:v>
+                  <c:v>94.934875000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>99.864418750000013</c:v>
+                  <c:v>96.681618750000013</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>106.85763968750001</c:v>
+                  <c:v>103.51569968750002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>105.20052167187502</c:v>
+                  <c:v>89.691484671875017</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>108.46054775546878</c:v>
+                  <c:v>82.176058905468778</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>100.88357514324223</c:v>
+                  <c:v>82.284861850742217</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.92775390040434</c:v>
+                  <c:v>68.399104943279326</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>92.774141595424567</c:v>
+                  <c:v>51.819060190443295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8081,10 +8081,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8349,14 +8345,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:Q5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="7.140625" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="17" width="8.7109375" customWidth="1"/>
+    <col min="1" max="3" width="7.1328125" customWidth="1"/>
+    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="17" width="8.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F2" s="3">
         <v>45292</v>
       </c>
@@ -8394,7 +8390,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>-20</v>
       </c>
@@ -8412,50 +8408,50 @@
       </c>
       <c r="G3" s="2">
         <f ca="1">(1+$C3)*F3 + RANDBETWEEN($A3,$B3)</f>
-        <v>197.25</v>
+        <v>195.25</v>
       </c>
       <c r="H3" s="2">
         <f t="shared" ref="H3:Q3" ca="1" si="0">(1+$C3)*G3 + RANDBETWEEN($A3,$B3)</f>
-        <v>191.11250000000001</v>
+        <v>202.01250000000002</v>
       </c>
       <c r="I3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>197.66812500000003</v>
+        <v>201.11312500000003</v>
       </c>
       <c r="J3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>196.55153125000004</v>
+        <v>206.16878125000002</v>
       </c>
       <c r="K3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>208.37910781250005</v>
+        <v>216.47722031250004</v>
       </c>
       <c r="L3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>217.79806320312505</v>
+        <v>228.30108132812504</v>
       </c>
       <c r="M3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>223.6879663632813</v>
+        <v>235.71613539453131</v>
       </c>
       <c r="N3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>215.87236468144539</v>
+        <v>248.50194216425788</v>
       </c>
       <c r="O3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>229.66598291551767</v>
+        <v>242.92703927247078</v>
       </c>
       <c r="P3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>232.14928206129358</v>
+        <v>247.07339123609432</v>
       </c>
       <c r="Q3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>232.75674616435828</v>
+        <v>255.42706079789906</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>-10</v>
       </c>
@@ -8473,50 +8469,50 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:Q5" ca="1" si="1">(1+$C4)*F4 + RANDBETWEEN($A4,$B4)</f>
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>168.15</v>
+        <v>160.9</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>179.5575</v>
+        <v>162.94500000000002</v>
       </c>
       <c r="J4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>185.53537500000002</v>
+        <v>175.09225000000004</v>
       </c>
       <c r="K4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>192.81214375000002</v>
+        <v>182.84686250000004</v>
       </c>
       <c r="L4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>194.45275093750004</v>
+        <v>186.98920562500004</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>207.17538848437505</v>
+        <v>194.33866590625004</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>222.53415790859381</v>
+        <v>198.05559920156256</v>
       </c>
       <c r="O4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>237.6608658040235</v>
+        <v>207.95837916164069</v>
       </c>
       <c r="P4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>245.54390909422469</v>
+        <v>221.35629811972274</v>
       </c>
       <c r="Q4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>256.82110454893592</v>
+        <v>233.42411302570889</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>-20</v>
       </c>
@@ -8534,47 +8530,47 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>94.350000000000009</v>
+        <v>115.95</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>96.06750000000001</v>
+        <v>103.7475</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>99.870875000000012</v>
+        <v>94.934875000000005</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>99.864418750000013</v>
+        <v>96.681618750000013</v>
       </c>
       <c r="L5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>106.85763968750001</v>
+        <v>103.51569968750002</v>
       </c>
       <c r="M5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>105.20052167187502</v>
+        <v>89.691484671875017</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>108.46054775546878</v>
+        <v>82.176058905468778</v>
       </c>
       <c r="O5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>100.88357514324223</v>
+        <v>82.284861850742217</v>
       </c>
       <c r="P5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>96.92775390040434</v>
+        <v>68.399104943279326</v>
       </c>
       <c r="Q5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>92.774141595424567</v>
+        <v>51.819060190443295</v>
       </c>
     </row>
   </sheetData>
@@ -8623,7 +8619,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B838CC0-3241-4CF6-86BF-BD8855F248AB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
